--- a/backend/data/financials_by_company/1H3.SI.xlsx
+++ b/backend/data/financials_by_company/1H3.SI.xlsx
@@ -4335,10 +4335,8 @@
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>577177</t>
-        </is>
+      <c r="D2" t="n">
+        <v>577177</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4552,7 +4550,7 @@
         <v>-12908000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>1.062</v>
@@ -4719,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ2" t="n">
         <v>0</v>
